--- a/config/explorer/explorer_effect.xlsx
+++ b/config/explorer/explorer_effect.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="explorer_effect" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="explorer_effect" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1165,48 +1165,37 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1316,27 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" s="1" t="n"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1354,7 +1323,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1365,19 +1333,9 @@
           <t>&lt;2.4%;2.8%;3.2%;3.6%;4%;4.4%;4.8%;5.2%;5.6%;6%;6.4%;6.8%;7.2%;7.6%;8%;8.4%;8.8%;9.2%;9.6%;10%;&gt;</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#全体伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1417,7 +1375,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1480,7 +1437,7 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1520,7 +1477,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1531,19 +1487,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1583,7 +1529,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1594,19 +1539,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1646,7 +1581,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1657,19 +1591,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1709,7 +1633,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1720,19 +1643,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1756,28 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -1794,7 +1686,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>7</t>
@@ -1815,17 +1706,9 @@
           <t>&lt;2.4%;2.8%;3.2%;3.6%;4%;4.4%;4.8%;5.2%;5.6%;6%;6.4%;6.8%;7.2%;7.6%;8%;8.4%;8.8%;9.2%;9.6%;10%;&gt;</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#全体伙伴%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1865,7 +1748,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1928,7 +1810,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1968,7 +1850,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>7</t>
@@ -1989,17 +1870,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2039,7 +1912,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>7</t>
@@ -2060,17 +1932,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2110,7 +1974,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>7</t>
@@ -2131,17 +1994,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2181,7 +2036,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>7</t>
@@ -2202,17 +2056,9 @@
           <t>&lt;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;1%;&gt;</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s#C0x5B545B##F40#、%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2236,28 +2082,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -2274,7 +2099,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>32</t>
@@ -2285,19 +2109,9 @@
           <t>&lt;250;300;350;400;450;500;550;600;650;700;750;800;850;900;950;1000;1050;1100;1150;1200;&gt;</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#全体伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2337,7 +2151,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2400,7 +2213,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2440,7 +2253,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>32</t>
@@ -2451,19 +2263,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2503,7 +2305,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>32</t>
@@ -2514,19 +2315,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2566,7 +2357,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>32</t>
@@ -2577,19 +2367,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2629,7 +2409,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>32</t>
@@ -2640,19 +2419,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2692,7 +2461,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>32</t>
@@ -2703,19 +2471,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2739,28 +2497,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
@@ -2777,7 +2514,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>34</t>
@@ -2788,19 +2524,9 @@
           <t>&lt;250;300;350;400;450;500;550;600;650;700;750;800;850;900;950;1000;1050;1100;1150;1200;&gt;</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#全体伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2840,7 +2566,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>1</t>
@@ -2903,7 +2628,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2943,7 +2668,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>34</t>
@@ -2954,19 +2678,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3006,7 +2720,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>34</t>
@@ -3017,19 +2730,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3069,7 +2772,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>34</t>
@@ -3080,19 +2782,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3132,7 +2824,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>34</t>
@@ -3143,19 +2834,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3195,7 +2876,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>34</t>
@@ -3206,19 +2886,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3242,28 +2912,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
@@ -3280,7 +2929,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>23</t>
@@ -3291,19 +2939,9 @@
           <t>&lt;250;300;350;400;450;500;550;600;650;700;750;800;850;900;950;1000;1050;1100;1150;1200;&gt;</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#全体伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3343,7 +2981,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>1</t>
@@ -3406,7 +3043,7 @@
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3446,7 +3083,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>23</t>
@@ -3457,19 +3093,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3509,7 +3135,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>23</t>
@@ -3520,19 +3145,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3572,7 +3187,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>23</t>
@@ -3583,19 +3197,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3635,7 +3239,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>23</t>
@@ -3646,19 +3249,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3698,7 +3291,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>23</t>
@@ -3709,19 +3301,9 @@
           <t>&lt;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;100;&gt;</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3745,28 +3327,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -3788,18 +3349,6 @@
           <t>61506</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr">
         <is>
           <t>%s</t>
@@ -3842,7 +3391,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>1</t>
@@ -3905,7 +3453,7 @@
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3945,7 +3493,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>17</t>
@@ -3956,19 +3503,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4008,7 +3545,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>19</t>
@@ -4019,19 +3555,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4071,7 +3597,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>33</t>
@@ -4082,19 +3607,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4134,7 +3649,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>35</t>
@@ -4145,19 +3659,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4197,7 +3701,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>16</t>
@@ -4208,19 +3711,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4244,28 +3737,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -4287,18 +3759,6 @@
           <t>61509</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr">
         <is>
           <t>%s</t>
@@ -4341,7 +3801,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>1</t>
@@ -4404,7 +3863,7 @@
       </c>
       <c r="Q52" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4444,7 +3903,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>11</t>
@@ -4455,19 +3913,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4507,7 +3955,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>12</t>
@@ -4518,19 +3965,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4570,7 +4007,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>32</t>
@@ -4581,19 +4017,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4633,7 +4059,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>34</t>
@@ -4644,19 +4069,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4696,7 +4111,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>14</t>
@@ -4707,19 +4121,9 @@
           <t>&lt;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;300;&gt;</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -4743,28 +4147,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-    </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
@@ -4786,18 +4169,6 @@
           <t>61507</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>%s</t>
@@ -4840,7 +4211,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>1</t>
@@ -4903,7 +4273,7 @@
       </c>
       <c r="Q60" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4943,7 +4313,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>93</t>
@@ -4954,19 +4323,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5006,7 +4365,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>28</t>
@@ -5017,19 +4375,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5069,7 +4417,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>25</t>
@@ -5080,19 +4427,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5132,7 +4469,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>16</t>
@@ -5143,19 +4479,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
       <c r="Q64" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5195,7 +4521,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>23</t>
@@ -5206,19 +4531,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
       <c r="Q65" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5242,28 +4557,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
@@ -5285,18 +4579,6 @@
           <t>61511</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr">
         <is>
           <t>%s</t>
@@ -5339,7 +4621,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>1</t>
@@ -5402,7 +4683,7 @@
       </c>
       <c r="Q68" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#仲間全員の基礎属性+#F50##C0x5C9970#%s</t>
+          <t>#C0x5B545B##F40#所有伙伴的基础属性+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5442,7 +4723,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>92</t>
@@ -5453,19 +4733,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
       <c r="Q69" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+3で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+3中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -5505,7 +4775,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>15</t>
@@ -5516,19 +4785,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
       <c r="Q70" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+6で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+6中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -5568,7 +4827,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>24</t>
@@ -5579,19 +4837,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+9で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+9中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -5631,7 +4879,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>14</t>
@@ -5642,19 +4889,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
       <c r="Q72" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+12で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+12中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5694,7 +4931,6 @@
           <t>&lt;&gt;</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>22</t>
@@ -5705,19 +4941,9 @@
           <t>&lt;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;500;&gt;</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" s="1" t="inlineStr">
         <is>
-          <t>#C0x5B545B##F40#+15で解放: 仲間全員の%s+#F50##C0x5C9970#%s</t>
+          <t>在#C0x5B545B##F40#+15中解放：所有伙伴%s+#F50##C0x5C9970#%s</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
